--- a/ch_11_ai_assistance/ch_11_solution.xlsx
+++ b/ch_11_ai_assistance/ch_11_solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30403"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_11_ai_assistance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7619A3FC-488E-418D-9C04-DA4FAFA1CCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4154512A-49CE-494D-BC02-B2CCFEFF735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization userModified="1">
+    <initialization>
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -103,6 +103,16 @@
 model = sm.OLS(y, X, missing='drop').fit() 
 model.summary() 
 f"Rows in data: {len(mpg_df):,} / Rows used by model: {int(model.nobs):,}"</code>
+    </pythonScript>
+    <pythonScript>
+      <code>import statsmodels.formula.api as smf
+reg_df = mpg_df.dropna(subset=['horsepower']).copy()
+model = smf.ols(
+    'mpg ~ cylinders + displacement + horsepower'
+    ' + weight + acceleration + C(origin, Treatment(reference="usa"))',
+    data=reg_df
+).fit()
+model.summary2().tables[1]</code>
     </pythonScript>
   </pythonScripts>
 </python>
@@ -588,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M399"/>
+  <dimension ref="A1:P399"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -599,10 +609,10 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="10" max="10" width="21.265625" customWidth="1"/>
+    <col min="10" max="10" width="39.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -628,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>18</v>
       </c>
@@ -667,7 +677,7 @@
         <v>std</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>15</v>
       </c>
@@ -705,7 +715,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>18</v>
       </c>
@@ -743,7 +753,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>16</v>
       </c>
@@ -781,7 +791,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>17</v>
       </c>
@@ -819,7 +829,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>15</v>
       </c>
@@ -845,7 +855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>14</v>
       </c>
@@ -871,7 +881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>14</v>
       </c>
@@ -901,7 +911,7 @@
         <v>Rows in data: 398 / Rows used by model: 392</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>14</v>
       </c>
@@ -927,7 +937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>15</v>
       </c>
@@ -953,7 +963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>15</v>
       </c>
@@ -978,8 +988,30 @@
       <c r="H12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J12" t="str" cm="1">
+        <f t="array" ref="J12:P20">_xlfn._xlws.PY(2,0)</f>
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Coef.</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Std.Err.</v>
+      </c>
+      <c r="M12" t="str">
+        <v>t</v>
+      </c>
+      <c r="N12" t="str">
+        <v>P&gt;|t|</v>
+      </c>
+      <c r="O12" t="str">
+        <v>[0.025</v>
+      </c>
+      <c r="P12" t="str">
+        <v>0.975]</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>14</v>
       </c>
@@ -1004,8 +1036,29 @@
       <c r="H13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J13" t="str">
+        <v>Intercept</v>
+      </c>
+      <c r="K13">
+        <v>44.768791093939278</v>
+      </c>
+      <c r="L13">
+        <v>2.639845678008506</v>
+      </c>
+      <c r="M13">
+        <v>16.958866750011222</v>
+      </c>
+      <c r="N13">
+        <v>1.5069966434467596E-48</v>
+      </c>
+      <c r="O13">
+        <v>39.578429579547574</v>
+      </c>
+      <c r="P13">
+        <v>49.959152608330982</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>15</v>
       </c>
@@ -1030,8 +1083,29 @@
       <c r="H14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J14" t="str">
+        <v>C(origin, Treatment(reference="usa"))[T.europe]</v>
+      </c>
+      <c r="K14">
+        <v>1.1255450993376057</v>
+      </c>
+      <c r="L14">
+        <v>0.70155663166100612</v>
+      </c>
+      <c r="M14">
+        <v>1.6043538732899782</v>
+      </c>
+      <c r="N14">
+        <v>0.10945817115951426</v>
+      </c>
+      <c r="O14">
+        <v>-0.25382816155943866</v>
+      </c>
+      <c r="P14">
+        <v>2.5049183602346501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1056,8 +1130,29 @@
       <c r="H15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J15" t="str">
+        <v>C(origin, Treatment(reference="usa"))[T.japan]</v>
+      </c>
+      <c r="K15">
+        <v>2.9325396705706366</v>
+      </c>
+      <c r="L15">
+        <v>0.69556748674791657</v>
+      </c>
+      <c r="M15">
+        <v>4.2160390277606954</v>
+      </c>
+      <c r="N15">
+        <v>3.1035280798707416E-5</v>
+      </c>
+      <c r="O15">
+        <v>1.5649420325897265</v>
+      </c>
+      <c r="P15">
+        <v>4.3001373085515464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>24</v>
       </c>
@@ -1082,8 +1177,29 @@
       <c r="H16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J16" t="str">
+        <v>cylinders</v>
+      </c>
+      <c r="K16">
+        <v>-0.56618762850693949</v>
+      </c>
+      <c r="L16">
+        <v>0.4042069027992049</v>
+      </c>
+      <c r="M16">
+        <v>-1.4007371585838568</v>
+      </c>
+      <c r="N16">
+        <v>0.16210023902885551</v>
+      </c>
+      <c r="O16">
+        <v>-1.3609234608390675</v>
+      </c>
+      <c r="P16">
+        <v>0.22854820382518859</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>22</v>
       </c>
@@ -1108,8 +1224,29 @@
       <c r="H17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J17" t="str">
+        <v>displacement</v>
+      </c>
+      <c r="K17">
+        <v>1.1427022236515993E-2</v>
+      </c>
+      <c r="L17">
+        <v>9.5736696280549916E-3</v>
+      </c>
+      <c r="M17">
+        <v>1.1935885277500988</v>
+      </c>
+      <c r="N17">
+        <v>0.2333758308072085</v>
+      </c>
+      <c r="O17">
+        <v>-7.3963532368730399E-3</v>
+      </c>
+      <c r="P17">
+        <v>3.0250397709905025E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>18</v>
       </c>
@@ -1134,8 +1271,29 @@
       <c r="H18" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J18" t="str">
+        <v>horsepower</v>
+      </c>
+      <c r="K18">
+        <v>-6.1333905587710721E-2</v>
+      </c>
+      <c r="L18">
+        <v>1.6867936195711444E-2</v>
+      </c>
+      <c r="M18">
+        <v>-3.6361238788242773</v>
+      </c>
+      <c r="N18">
+        <v>3.1449780493801301E-4</v>
+      </c>
+      <c r="O18">
+        <v>-9.4498983223416877E-2</v>
+      </c>
+      <c r="P18">
+        <v>-2.8168827952004559E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>21</v>
       </c>
@@ -1160,8 +1318,29 @@
       <c r="H19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J19" t="str">
+        <v>weight</v>
+      </c>
+      <c r="K19">
+        <v>-4.8119316563116805E-3</v>
+      </c>
+      <c r="L19">
+        <v>8.0894151921187974E-4</v>
+      </c>
+      <c r="M19">
+        <v>-5.9484295737468864</v>
+      </c>
+      <c r="N19">
+        <v>6.0967007570731061E-9</v>
+      </c>
+      <c r="O19">
+        <v>-6.4024408908811749E-3</v>
+      </c>
+      <c r="P19">
+        <v>-3.2214224217421861E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>27</v>
       </c>
@@ -1186,8 +1365,29 @@
       <c r="H20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J20" t="str">
+        <v>acceleration</v>
+      </c>
+      <c r="K20">
+        <v>-3.1984129141198303E-2</v>
+      </c>
+      <c r="L20">
+        <v>0.12325291338425248</v>
+      </c>
+      <c r="M20">
+        <v>-0.2594999847304606</v>
+      </c>
+      <c r="N20">
+        <v>0.79538855858806079</v>
+      </c>
+      <c r="O20">
+        <v>-0.27431919573072971</v>
+      </c>
+      <c r="P20">
+        <v>0.21035093744833314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>26</v>
       </c>
@@ -1213,7 +1413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>25</v>
       </c>
@@ -1239,7 +1439,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>24</v>
       </c>
@@ -1265,7 +1465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>25</v>
       </c>
@@ -1291,7 +1491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>26</v>
       </c>
@@ -1317,7 +1517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>21</v>
       </c>
@@ -1343,7 +1543,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -1369,7 +1569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -1395,7 +1595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>11</v>
       </c>
@@ -1421,7 +1621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>9</v>
       </c>
@@ -1447,7 +1647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -1473,7 +1673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
